--- a/data/travel_sheet_v3_reconciled.xlsx
+++ b/data/travel_sheet_v3_reconciled.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arezo-o\Downloads\ArezooHassannezhad\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020AC71F-4CEF-43EB-80E1-D42D9207A22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F902DFAC-564A-403E-98EA-C2E4FFE1A395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -424,13 +424,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor theme="4" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.249977111117893"/>
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,14 +453,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -766,10 +765,8 @@
   <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="16" style="5" customWidth="1"/>
-    <col min="9" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="32" style="5" customWidth="1"/>
+    <col min="1" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="32" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -795,7 +792,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -804,784 +801,784 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>640</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="3">
         <v>624</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>720</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="3">
         <v>693</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="J3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>890</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="3">
         <v>895</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="J4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>710</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="3">
         <v>711</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="J5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>410</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="3">
         <v>408</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="3" t="s">
+      <c r="J6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>680</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="3">
         <v>667</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="J7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <v>500</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="3">
         <v>483</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" s="6" t="s">
+      <c r="J8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="L8" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <v>540</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="3">
         <v>579</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="J9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <v>450</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="3">
         <v>431</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" s="6" t="s">
+      <c r="J10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="L10" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>380</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="3">
         <v>60</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="L11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <v>890</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="3">
         <v>935</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" s="6" t="s">
+      <c r="J12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="L12" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <v>930</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="3">
         <v>954</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="6"/>
-      <c r="L13" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="J13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <v>510</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="3">
         <v>484</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="J14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <v>900</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="3">
         <v>873</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K15" s="6"/>
-      <c r="L15" s="3" t="s">
+      <c r="J15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <v>690</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="3">
         <v>671</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" s="6"/>
-      <c r="L16" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="J16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="2">
         <v>430</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="3">
         <v>427</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K17" s="6" t="s">
+      <c r="J17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="L17" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="2">
         <v>450</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="3">
         <v>449</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="6" t="s">
+      <c r="J18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="L18" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="2">
         <v>430</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="3">
         <v>464</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K19" s="6"/>
-      <c r="L19" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="J19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="2">
         <v>940</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="3">
         <v>958</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K20" s="6" t="s">
+      <c r="J20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="L20" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="3">
         <v>560</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="3">
         <v>575</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="I21" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="J21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K21" s="6" t="s">
+      <c r="J21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="L21" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+      <c r="L21" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="4">
         <v>390</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="3">
         <v>410</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="J22" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K22" s="6" t="s">
+      <c r="J22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="L22" s="6" t="s">
+      <c r="L22" s="4" t="s">
         <v>20</v>
       </c>
     </row>

--- a/data/travel_sheet_v3_reconciled.xlsx
+++ b/data/travel_sheet_v3_reconciled.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arezo-o\Downloads\ArezooHassannezhad\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F902DFAC-564A-403E-98EA-C2E4FFE1A395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF9D9D1-B7EF-4C30-9DFF-902202B5101A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -453,13 +453,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -839,7 +838,7 @@
       <c r="J2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="2"/>
+      <c r="K2" s="4"/>
       <c r="L2" s="2" t="s">
         <v>20</v>
       </c>
@@ -875,7 +874,7 @@
       <c r="J3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="2"/>
+      <c r="K3" s="4"/>
       <c r="L3" s="2" t="s">
         <v>20</v>
       </c>
@@ -911,7 +910,7 @@
       <c r="J4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="2"/>
+      <c r="K4" s="4"/>
       <c r="L4" s="2" t="s">
         <v>20</v>
       </c>
@@ -947,7 +946,7 @@
       <c r="J5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="2"/>
+      <c r="K5" s="4"/>
       <c r="L5" s="2" t="s">
         <v>20</v>
       </c>
@@ -983,7 +982,7 @@
       <c r="J6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="2"/>
+      <c r="K6" s="4"/>
       <c r="L6" s="2" t="s">
         <v>45</v>
       </c>
@@ -1019,7 +1018,7 @@
       <c r="J7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="2"/>
+      <c r="K7" s="4"/>
       <c r="L7" s="2" t="s">
         <v>20</v>
       </c>
@@ -1055,7 +1054,7 @@
       <c r="J8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="4" t="s">
         <v>56</v>
       </c>
       <c r="L8" s="2" t="s">
@@ -1093,7 +1092,7 @@
       <c r="J9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="2"/>
+      <c r="K9" s="4"/>
       <c r="L9" s="2" t="s">
         <v>20</v>
       </c>
@@ -1129,7 +1128,7 @@
       <c r="J10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="4" t="s">
         <v>67</v>
       </c>
       <c r="L10" s="2" t="s">
@@ -1164,10 +1163,10 @@
       <c r="I11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="4" t="s">
         <v>74</v>
       </c>
       <c r="L11" s="2" t="s">
@@ -1205,7 +1204,7 @@
       <c r="J12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" s="4" t="s">
         <v>79</v>
       </c>
       <c r="L12" s="2" t="s">
@@ -1243,7 +1242,7 @@
       <c r="J13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="2"/>
+      <c r="K13" s="4"/>
       <c r="L13" s="2" t="s">
         <v>20</v>
       </c>
@@ -1279,7 +1278,7 @@
       <c r="J14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="2"/>
+      <c r="K14" s="4"/>
       <c r="L14" s="2" t="s">
         <v>20</v>
       </c>
@@ -1315,7 +1314,7 @@
       <c r="J15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="2"/>
+      <c r="K15" s="4"/>
       <c r="L15" s="2" t="s">
         <v>45</v>
       </c>
@@ -1351,7 +1350,7 @@
       <c r="J16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K16" s="2"/>
+      <c r="K16" s="4"/>
       <c r="L16" s="2" t="s">
         <v>20</v>
       </c>
@@ -1387,7 +1386,7 @@
       <c r="J17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="K17" s="4" t="s">
         <v>102</v>
       </c>
       <c r="L17" s="2" t="s">
@@ -1425,7 +1424,7 @@
       <c r="J18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" s="4" t="s">
         <v>105</v>
       </c>
       <c r="L18" s="2" t="s">
@@ -1463,7 +1462,7 @@
       <c r="J19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K19" s="2"/>
+      <c r="K19" s="4"/>
       <c r="L19" s="2" t="s">
         <v>20</v>
       </c>
@@ -1499,14 +1498,14 @@
       <c r="J20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="K20" s="4" t="s">
         <v>115</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>116</v>
       </c>
@@ -1537,14 +1536,14 @@
       <c r="J21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="K21" s="4" t="s">
         <v>120</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>121</v>
       </c>
